--- a/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475748</t>
+          <t>473398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487896</t>
+          <t>487919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439748</t>
+          <t>438536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456021</t>
+          <t>455456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>921450</t>
+          <t>919148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941231</t>
+          <t>940502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30338</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59825</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696612</t>
+          <t>696590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>716157</t>
+          <t>715814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595156</t>
+          <t>596085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>613127</t>
+          <t>613408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1298148</t>
+          <t>1298190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1325284</t>
+          <t>1324980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>31191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58344</t>
+          <t>56803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>59645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95955</t>
+          <t>93659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590711</t>
+          <t>591541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615871</t>
+          <t>615732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629365</t>
+          <t>630906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656985</t>
+          <t>656518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1229539</t>
+          <t>1231835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266061</t>
+          <t>1265849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50081</t>
+          <t>49071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70743</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>74946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111317</t>
+          <t>114208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>466349</t>
+          <t>467359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490824</t>
+          <t>491009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442658</t>
+          <t>442100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471216</t>
+          <t>470635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>918515</t>
+          <t>915624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>956281</t>
+          <t>954886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62684</t>
+          <t>61431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53780</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71647</t>
+          <t>71009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108166</t>
+          <t>106488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323182</t>
+          <t>324435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349850</t>
+          <t>349099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350206</t>
+          <t>349540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374801</t>
+          <t>373977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681686</t>
+          <t>683364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718205</t>
+          <t>718843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>49225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56681</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245231</t>
+          <t>245464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267156</t>
+          <t>266910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>292713</t>
+          <t>293709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315131</t>
+          <t>314408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>545031</t>
+          <t>545907</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578000</t>
+          <t>576711</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>43660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>44338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>73748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72666</t>
+          <t>72405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107863</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166950</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>187003</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261899</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289893</t>
+          <t>289570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435928</t>
+          <t>435706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471125</t>
+          <t>471386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>189845</t>
+          <t>189776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>248188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>239778</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307359</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>448730</t>
+          <t>449897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>532442</t>
+          <t>534914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3019456</t>
+          <t>3019078</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3077421</t>
+          <t>3077490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3067562</t>
+          <t>3071937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3133390</t>
+          <t>3135143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6109745</t>
+          <t>6107273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6193457</t>
+          <t>6192290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36052</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>32449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59299</t>
+          <t>57632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421580</t>
+          <t>422953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>440527</t>
+          <t>441456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>394178</t>
+          <t>395128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413710</t>
+          <t>414063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>824029</t>
+          <t>825696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>850565</t>
+          <t>850879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57096</t>
+          <t>57500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63719</t>
+          <t>63810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>100038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>629991</t>
+          <t>629587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>655746</t>
+          <t>656678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556191</t>
+          <t>558757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>583456</t>
+          <t>582690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1197584</t>
+          <t>1196357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1232676</t>
+          <t>1232585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67013</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>54278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98190</t>
+          <t>98037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143125</t>
+          <t>139963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614850</t>
+          <t>616603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643620</t>
+          <t>645981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624840</t>
+          <t>622712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656857</t>
+          <t>655624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248640</t>
+          <t>1251802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293575</t>
+          <t>1293728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76501</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61609</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95716</t>
+          <t>95701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113689</t>
+          <t>113362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162649</t>
+          <t>159738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>537130</t>
+          <t>538047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568895</t>
+          <t>570185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520483</t>
+          <t>520498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>554590</t>
+          <t>555331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1067181</t>
+          <t>1070092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1116141</t>
+          <t>1116468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43055</t>
+          <t>43665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>73970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52153</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82755</t>
+          <t>81162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100054</t>
+          <t>101830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142367</t>
+          <t>145265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357511</t>
+          <t>354327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385242</t>
+          <t>384632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365045</t>
+          <t>366638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395647</t>
+          <t>399213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733730</t>
+          <t>730832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776043</t>
+          <t>774267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64896</t>
+          <t>62563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36451</t>
+          <t>36799</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62159</t>
+          <t>62774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77645</t>
+          <t>79533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117724</t>
+          <t>119534</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244890</t>
+          <t>247223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274932</t>
+          <t>275366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291837</t>
+          <t>291222</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317545</t>
+          <t>317197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>546058</t>
+          <t>544248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586137</t>
+          <t>584249</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38616</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67828</t>
+          <t>67975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70003</t>
+          <t>71873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104430</t>
+          <t>105834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118014</t>
+          <t>116461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164768</t>
+          <t>162176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182023</t>
+          <t>181876</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211235</t>
+          <t>211056</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>284549</t>
+          <t>283145</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318976</t>
+          <t>317106</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>474062</t>
+          <t>476654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>520816</t>
+          <t>522369</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291937</t>
+          <t>290109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>365686</t>
+          <t>363057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>372104</t>
+          <t>371795</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>450408</t>
+          <t>454340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>683949</t>
+          <t>684420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>785386</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3057926</t>
+          <t>3060555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3131675</t>
+          <t>3133503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3106006</t>
+          <t>3102074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3184310</t>
+          <t>3184619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6194641</t>
+          <t>6187418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6296078</t>
+          <t>6295607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>37510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>387787</t>
+          <t>387331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405968</t>
+          <t>405892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377915</t>
+          <t>377884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390350</t>
+          <t>390182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>773195</t>
+          <t>773717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>794228</t>
+          <t>794086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33042</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58661</t>
+          <t>56517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>550266</t>
+          <t>550879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>569244</t>
+          <t>568462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531226</t>
+          <t>530406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547912</t>
+          <t>547840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1085310</t>
+          <t>1087454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111870</t>
+          <t>1111929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48067</t>
+          <t>48168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82856</t>
+          <t>85835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624713</t>
+          <t>625606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647157</t>
+          <t>647439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611350</t>
+          <t>611249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634064</t>
+          <t>632844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1244585</t>
+          <t>1241606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275615</t>
+          <t>1275082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47723</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80527</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39942</t>
+          <t>39844</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68049</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94919</t>
+          <t>95277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138990</t>
+          <t>139432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562211</t>
+          <t>562080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595015</t>
+          <t>592496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>580001</t>
+          <t>579108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608108</t>
+          <t>608206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151798</t>
+          <t>1151356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1195869</t>
+          <t>1195511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66411</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56885</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90949</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>104594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148723</t>
+          <t>149896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410341</t>
+          <t>410037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438864</t>
+          <t>438923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404731</t>
+          <t>402996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438795</t>
+          <t>436385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823710</t>
+          <t>822537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871787</t>
+          <t>867839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44158</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,82 +8421,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>34991</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>60457</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>78081</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>62699</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>94060</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>13,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>45821</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>33935</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>60716</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>78081</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>60312</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>95904</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290172</t>
+          <t>290676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311296</t>
+          <t>312160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,82 +8534,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>331941</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>317305</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>342771</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>87,87%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>84,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>634011</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>618032</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>649393</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>89,03%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>86,79%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>331941</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>317046</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>343827</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>83,93%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>634011</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>616188</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>651780</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,53%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52920</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87229</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>72908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>110767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>224732</t>
+          <t>224315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241753</t>
+          <t>241627</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312940</t>
+          <t>310643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347249</t>
+          <t>346345</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546007</t>
+          <t>546400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583587</t>
+          <t>584259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>207562</t>
+          <t>206871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>272160</t>
+          <t>269362</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274838</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>343640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>501359</t>
+          <t>500086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591663</t>
+          <t>596343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3105464</t>
+          <t>3108262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3170062</t>
+          <t>3170753</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3193951</t>
+          <t>3193856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3262658</t>
+          <t>3261798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6323456</t>
+          <t>6318776</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6413760</t>
+          <t>6415033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74389</t>
+          <t>74419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350449</t>
+          <t>351923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382648</t>
+          <t>382176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269271</t>
+          <t>270005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295953</t>
+          <t>295918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>632930</t>
+          <t>632900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>673189</t>
+          <t>671610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>67809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>46005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>56330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103217</t>
+          <t>103064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350934</t>
+          <t>351746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386083</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464716</t>
+          <t>464525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492895</t>
+          <t>492100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>826868</t>
+          <t>827021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873925</t>
+          <t>873755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>44360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32534</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,47 +10406,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>76964</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>61936</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>94674</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>76964</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>58947</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>92783</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489536</t>
+          <t>488685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511667</t>
+          <t>512354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530765</t>
+          <t>531193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>557014</t>
+          <t>557711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,47 +10519,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>94,6%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1045629</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1027919</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1060657</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>94,48%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1045629</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1029810</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1063646</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137309</t>
+          <t>136427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67972</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>99336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107907</t>
+          <t>110395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220089</t>
+          <t>219972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>746949</t>
+          <t>747831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>844323</t>
+          <t>848713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606540</t>
+          <t>606811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638175</t>
+          <t>636034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1370316</t>
+          <t>1370433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1482498</t>
+          <t>1480010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88262</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>127075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57875</t>
+          <t>57039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81192</t>
+          <t>80161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152211</t>
+          <t>151833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194521</t>
+          <t>193389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434540</t>
+          <t>430979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469792</t>
+          <t>467344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462823</t>
+          <t>463854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486140</t>
+          <t>486976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>907548</t>
+          <t>908680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>949858</t>
+          <t>950236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74415</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102918</t>
+          <t>103296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>468152</t>
+          <t>478204</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162407</t>
+          <t>161872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>631511</t>
+          <t>653461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292358</t>
+          <t>294461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316662</t>
+          <t>316295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139498</t>
+          <t>129446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>504732</t>
+          <t>504354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342912</t>
+          <t>320962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>812016</t>
+          <t>812551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>68795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93488</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139525</t>
+          <t>138536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167274</t>
+          <t>166182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214440</t>
+          <t>214842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251453</t>
+          <t>251348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>187801</t>
+          <t>188771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211136</t>
+          <t>212494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257323</t>
+          <t>258415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285072</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>454433</t>
+          <t>454538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>491446</t>
+          <t>491044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,56%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>351263</t>
+          <t>338505</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>498687</t>
+          <t>500210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>499800</t>
+          <t>496321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1225374</t>
+          <t>1231422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>928987</t>
+          <t>927262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1976213</t>
+          <t>1857005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2938406</t>
+          <t>2936883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3085830</t>
+          <t>3098588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2470313</t>
+          <t>2464265</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3195887</t>
+          <t>3199366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5156566</t>
+          <t>5275774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6203792</t>
+          <t>6205517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473398</t>
+          <t>475629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487919</t>
+          <t>488533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438536</t>
+          <t>439224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>455456</t>
+          <t>456179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>919148</t>
+          <t>920135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940502</t>
+          <t>940731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35889</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29409</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696590</t>
+          <t>697512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>715814</t>
+          <t>715573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>596085</t>
+          <t>594587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>613408</t>
+          <t>612575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1298190</t>
+          <t>1297251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1324980</t>
+          <t>1324573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>21616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56803</t>
+          <t>56854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59645</t>
+          <t>59595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93659</t>
+          <t>95239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>591541</t>
+          <t>591599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615732</t>
+          <t>616170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630906</t>
+          <t>630855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656518</t>
+          <t>656855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1231835</t>
+          <t>1230255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1265849</t>
+          <t>1265899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>49345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71301</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74946</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114208</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>467359</t>
+          <t>467085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>491009</t>
+          <t>490964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442100</t>
+          <t>442323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470635</t>
+          <t>470641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915624</t>
+          <t>917673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>954886</t>
+          <t>956800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>35472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>29257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54446</t>
+          <t>54939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71009</t>
+          <t>72628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106488</t>
+          <t>108729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324435</t>
+          <t>325102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349099</t>
+          <t>350394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>349540</t>
+          <t>349047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373977</t>
+          <t>374729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>683364</t>
+          <t>681123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718843</t>
+          <t>717224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46283</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49225</t>
+          <t>50626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88774</t>
+          <t>89164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245464</t>
+          <t>244546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266910</t>
+          <t>267236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293709</t>
+          <t>292308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>314408</t>
+          <t>314504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>545907</t>
+          <t>545517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>576711</t>
+          <t>576921</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>22908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44338</t>
+          <t>43230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73748</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72405</t>
+          <t>73819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166223</t>
+          <t>167485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187003</t>
+          <t>186975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260160</t>
+          <t>260710</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289570</t>
+          <t>290678</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435706</t>
+          <t>435188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471386</t>
+          <t>469972</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>189776</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>248188</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239778</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449897</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>534914</t>
+          <t>532244</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3019078</t>
+          <t>3016894</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3077490</t>
+          <t>3078028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3071937</t>
+          <t>3068995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3135143</t>
+          <t>3130583</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6107273</t>
+          <t>6109943</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6192290</t>
+          <t>6193990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57632</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422953</t>
+          <t>424035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>441456</t>
+          <t>442278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>395128</t>
+          <t>395170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414063</t>
+          <t>414319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>825696</t>
+          <t>824873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>850879</t>
+          <t>850000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>30971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>50392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63810</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100038</t>
+          <t>99170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>629587</t>
+          <t>631260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>656678</t>
+          <t>656116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558757</t>
+          <t>558916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>582690</t>
+          <t>583975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1196357</t>
+          <t>1197225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1232585</t>
+          <t>1232036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65260</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54278</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>85509</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98037</t>
+          <t>98268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139963</t>
+          <t>140996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616603</t>
+          <t>616471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645981</t>
+          <t>644530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>622712</t>
+          <t>624393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655624</t>
+          <t>656719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251802</t>
+          <t>1250769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293728</t>
+          <t>1293497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>45040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>75017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>62233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95701</t>
+          <t>96500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113362</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159738</t>
+          <t>162075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538047</t>
+          <t>538614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570185</t>
+          <t>568591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520498</t>
+          <t>519699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>555331</t>
+          <t>553966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070092</t>
+          <t>1067755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1116468</t>
+          <t>1114354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43665</t>
+          <t>43327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81162</t>
+          <t>81236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101830</t>
+          <t>102005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145265</t>
+          <t>141956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>354327</t>
+          <t>356157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384632</t>
+          <t>384970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366638</t>
+          <t>366564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399213</t>
+          <t>397054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>730832</t>
+          <t>734141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>774267</t>
+          <t>774092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62563</t>
+          <t>64100</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36799</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79533</t>
+          <t>79530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119534</t>
+          <t>117554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247223</t>
+          <t>245686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275366</t>
+          <t>273832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291222</t>
+          <t>289129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317197</t>
+          <t>317412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544248</t>
+          <t>546228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584249</t>
+          <t>584252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>37858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71873</t>
+          <t>71675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105834</t>
+          <t>105557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116461</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162176</t>
+          <t>162382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181876</t>
+          <t>182879</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211056</t>
+          <t>211993</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283145</t>
+          <t>283422</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>317106</t>
+          <t>317304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476654</t>
+          <t>476448</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>522369</t>
+          <t>520849</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>290109</t>
+          <t>291578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>363057</t>
+          <t>364317</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371795</t>
+          <t>371725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>454340</t>
+          <t>453782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>684420</t>
+          <t>683989</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>793306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3060555</t>
+          <t>3059295</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3133503</t>
+          <t>3132034</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3102074</t>
+          <t>3102632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3184619</t>
+          <t>3184689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6187418</t>
+          <t>6186721</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6295607</t>
+          <t>6296038</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>387331</t>
+          <t>389298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405892</t>
+          <t>406109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377884</t>
+          <t>377518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390182</t>
+          <t>390245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>773717</t>
+          <t>772619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>794086</t>
+          <t>792671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>54367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>550879</t>
+          <t>551368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>568462</t>
+          <t>569667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>530406</t>
+          <t>528912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547840</t>
+          <t>547395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1087454</t>
+          <t>1089604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111929</t>
+          <t>1113519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42419</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52359</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>84011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625606</t>
+          <t>624134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647439</t>
+          <t>646672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611249</t>
+          <t>610685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>632844</t>
+          <t>633924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241606</t>
+          <t>1243430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275082</t>
+          <t>1275110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>48523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>80263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>40921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,47 +7770,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>116057</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>95635</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>137340</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>10,64%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>116057</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>95277</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>139432</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562080</t>
+          <t>562475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592496</t>
+          <t>594215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579108</t>
+          <t>578297</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608206</t>
+          <t>607129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,47 +7883,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1174731</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1153448</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1195153</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>89,36%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1174731</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1151356</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1195511</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66715</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59295</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92684</t>
+          <t>90971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104594</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410037</t>
+          <t>409397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438923</t>
+          <t>438802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402996</t>
+          <t>404709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>436385</t>
+          <t>437104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822537</t>
+          <t>825762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>867839</t>
+          <t>868501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62699</t>
+          <t>63907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94060</t>
+          <t>98170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290676</t>
+          <t>290499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312160</t>
+          <t>311213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317305</t>
+          <t>317631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342771</t>
+          <t>344298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618032</t>
+          <t>613922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>649393</t>
+          <t>648185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53824</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>87918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72908</t>
+          <t>74465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110767</t>
+          <t>112094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>224315</t>
+          <t>223776</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241627</t>
+          <t>241522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310643</t>
+          <t>312251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346345</t>
+          <t>347802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546400</t>
+          <t>545073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>584259</t>
+          <t>582702</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206871</t>
+          <t>204528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>269362</t>
+          <t>268352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>343640</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>500086</t>
+          <t>501779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>596343</t>
+          <t>593632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3108262</t>
+          <t>3109272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3170753</t>
+          <t>3173096</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3193856</t>
+          <t>3192128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3261798</t>
+          <t>3261719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6318776</t>
+          <t>6321487</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6415033</t>
+          <t>6413340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,67 +9700,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>54649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>60561</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>42240</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>84210</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>52144</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35709</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>74419</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>370763</t>
+          <t>377459</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>351923</t>
+          <t>361102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382176</t>
+          <t>389972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,67 +9813,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284412</t>
+          <t>327137</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270005</t>
+          <t>307863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295918</t>
+          <t>340810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>704596</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>680947</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>722917</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>94,48%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>632900</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>671610</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>394119</t>
+          <t>402645</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394119</t>
+          <t>402645</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394119</t>
+          <t>402645</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>707319</t>
+          <t>765157</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>707319</t>
+          <t>765157</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>707319</t>
+          <t>765157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>34505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67809</t>
+          <t>74836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>34424</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>23802</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46005</t>
+          <t>47303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79187</t>
+          <t>84913</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>64993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103064</t>
+          <t>111352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>371285</t>
+          <t>418393</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351746</t>
+          <t>394047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387055</t>
+          <t>434378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>479613</t>
+          <t>465719</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464525</t>
+          <t>452840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492100</t>
+          <t>476341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>850898</t>
+          <t>884113</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827021</t>
+          <t>857674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873755</t>
+          <t>904033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>419555</t>
+          <t>468883</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419555</t>
+          <t>468883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>419555</t>
+          <t>468883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510530</t>
+          <t>500143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510530</t>
+          <t>500143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510530</t>
+          <t>500143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>930085</t>
+          <t>969026</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>930085</t>
+          <t>969026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>930085</t>
+          <t>969026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45734</t>
+          <t>53819</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>66023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76964</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>71626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94674</t>
+          <t>105523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>501815</t>
+          <t>581810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488685</t>
+          <t>567690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512354</t>
+          <t>592575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>543814</t>
+          <t>566862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531193</t>
+          <t>554658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>557711</t>
+          <t>577257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1045629</t>
+          <t>1148672</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1027919</t>
+          <t>1132601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1060657</t>
+          <t>1166498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533045</t>
+          <t>617443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533045</t>
+          <t>617443</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533045</t>
+          <t>617443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>589548</t>
+          <t>620681</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>589548</t>
+          <t>620681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>589548</t>
+          <t>620681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1122593</t>
+          <t>1238124</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1122593</t>
+          <t>1238124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1122593</t>
+          <t>1238124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92294</t>
+          <t>98222</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>81348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>119936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>91422</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70113</t>
+          <t>79185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99336</t>
+          <t>107071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>176667</t>
+          <t>189643</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110395</t>
+          <t>168281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219972</t>
+          <t>215189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>791964</t>
+          <t>598649</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>747831</t>
+          <t>576935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848713</t>
+          <t>615523</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>621774</t>
+          <t>637773</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606811</t>
+          <t>622124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>636034</t>
+          <t>650010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1413738</t>
+          <t>1236423</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1370433</t>
+          <t>1210877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1480010</t>
+          <t>1257785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>884258</t>
+          <t>696871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>884258</t>
+          <t>696871</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>884258</t>
+          <t>696871</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>706147</t>
+          <t>729195</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>706147</t>
+          <t>729195</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>706147</t>
+          <t>729195</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1590405</t>
+          <t>1426066</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1590405</t>
+          <t>1426066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1590405</t>
+          <t>1426066</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>110711</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127075</t>
+          <t>131010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>68423</t>
+          <t>79172</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57039</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80161</t>
+          <t>92742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>173270</t>
+          <t>189883</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151833</t>
+          <t>168637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193389</t>
+          <t>214287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>453207</t>
+          <t>495314</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430979</t>
+          <t>475015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467344</t>
+          <t>511703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>475592</t>
+          <t>525606</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>463854</t>
+          <t>512036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486976</t>
+          <t>537287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>928799</t>
+          <t>1020920</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>908680</t>
+          <t>996516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>950236</t>
+          <t>1042166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558054</t>
+          <t>606025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558054</t>
+          <t>606025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558054</t>
+          <t>606025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544015</t>
+          <t>604778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544015</t>
+          <t>604778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544015</t>
+          <t>604778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>1210803</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>1210803</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>1210803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>67175</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>276398</t>
+          <t>78741</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103296</t>
+          <t>67942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>478204</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>337667</t>
+          <t>145916</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>130131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>653461</t>
+          <t>164738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>305504</t>
+          <t>338419</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294461</t>
+          <t>325580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316295</t>
+          <t>350866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>331252</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129446</t>
+          <t>348411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>504354</t>
+          <t>370458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>636756</t>
+          <t>698078</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320962</t>
+          <t>679256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>812551</t>
+          <t>713863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366773</t>
+          <t>405594</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366773</t>
+          <t>405594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366773</t>
+          <t>405594</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607650</t>
+          <t>438400</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607650</t>
+          <t>438400</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607650</t>
+          <t>438400</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974423</t>
+          <t>843994</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974423</t>
+          <t>843994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974423</t>
+          <t>843994</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>74300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>101188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>151994</t>
+          <t>166305</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166182</t>
+          <t>182745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,27 +11793,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>232935</t>
+          <t>253599</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214842</t>
+          <t>234870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251348</t>
+          <t>274795</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>200348</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188771</t>
+          <t>207244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212494</t>
+          <t>234132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>272603</t>
+          <t>296976</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258415</t>
+          <t>280536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286061</t>
+          <t>312220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,22 +11906,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>472951</t>
+          <t>518114</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>454538</t>
+          <t>496918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>491044</t>
+          <t>536843</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281289</t>
+          <t>308432</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281289</t>
+          <t>308432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281289</t>
+          <t>308432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424597</t>
+          <t>463281</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424597</t>
+          <t>463281</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424597</t>
+          <t>463281</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705886</t>
+          <t>771713</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705886</t>
+          <t>771713</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705886</t>
+          <t>771713</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338505</t>
+          <t>428364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>500210</t>
+          <t>515490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>496321</t>
+          <t>503319</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1231422</t>
+          <t>576475</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>927262</t>
+          <t>957866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1857005</t>
+          <t>1073169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2994887</t>
+          <t>3031181</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2936883</t>
+          <t>2990402</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3098588</t>
+          <t>3077528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3009059</t>
+          <t>3179733</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2464265</t>
+          <t>3142515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3199366</t>
+          <t>3215671</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6003946</t>
+          <t>6210915</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5275774</t>
+          <t>6151713</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6205517</t>
+          <t>6267016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
